--- a/Data/EXCEL/Transfer/bzPerformance/2024Q4/5233-bzPerformance-2024Q4.xlsx
+++ b/Data/EXCEL/Transfer/bzPerformance/2024Q4/5233-bzPerformance-2024Q4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\2024Q4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83A2459F-42DE-4DE8-9699-4F7A2A2ED097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{627CCD78-747B-43A3-8F26-70983B46F424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="840" windowWidth="17640" windowHeight="14310" xr2:uid="{EC9060CC-5355-4FB6-A67D-6A2B3B9CAA33}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{66595B5A-5304-4E66-A240-27274BC9AE36}"/>
   </bookViews>
   <sheets>
     <sheet name="5233-bzPerformance-2024Q4" sheetId="2" r:id="rId1"/>
@@ -1323,14 +1323,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C9FD060-DD9A-4015-A088-377772EE3193}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3C0432-878C-4147-B0DB-92E5BA916A10}">
   <dimension ref="A1:U19"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="17" width="7.08984375" customWidth="1"/>
-    <col min="18" max="18" width="7.36328125" customWidth="1"/>
-    <col min="19" max="20" width="7.08984375" customWidth="1"/>
-    <col min="21" max="21" width="8.90625" customWidth="1"/>
+    <col min="1" max="17" width="11.6328125" customWidth="1"/>
+    <col min="18" max="18" width="12.08984375" customWidth="1"/>
+    <col min="19" max="20" width="11.6328125" customWidth="1"/>
+    <col min="21" max="21" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
